--- a/docs/New-Outlet-Setup.xlsx
+++ b/docs/New-Outlet-Setup.xlsx
@@ -10,18 +10,17 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1. Owner &amp; Group" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Outlet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3. Subscription" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4. Staff (Mgr-CCO)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5. Attendants" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6. Tanks" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7. Pumps" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="8. Nozzles" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="9. Fuel Prices" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10. Shift Timings" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11. Credit Customers" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12. Credit Slip Books" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13. Products" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14. Corporate Drivers" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="3. Staff (Mgr-CCO)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. Attendants" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Tanks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. Pumps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7. Nozzles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8. Fuel Prices" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9. Shift Timings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10. Credit Customers" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11. Credit Slip Books" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12. Products" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13. Defaults" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -371,22 +370,27 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>1, 2 or 3.</t>
+        <t>The account name.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>e.g. Morning / Afternoon / Night.</t>
+        <t>10 digits. Used to dedupe within the outlet.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>24-hour HH:MM, e.g. 06:00.</t>
+        <t>Amount owed at go-live. 0 or blank if none.</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>24-hour HH:MM, e.g. 14:00.</t>
+        <t>Per-outlet credit ceiling. Optional.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>For their GST invoices. Optional.</t>
       </text>
     </comment>
   </commentList>
@@ -401,27 +405,42 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>The account name.</t>
+        <t>Which credit customer this booklet is issued to. Must match a company on tab 10.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>10 digits. Used to dedupe within the outlet.</t>
+        <t>Optional printed book id / name. Free text.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Amount owed at go-live. 0 or blank if none.</t>
+        <t>The FIRST coupon number in the book, e.g. 17701. Ranges must not overlap another book at this outlet.</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>Per-outlet credit ceiling. Optional.</t>
+        <t>The LAST coupon number in the book, e.g. 17800. Must be ≥ series start.</t>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>For their GST invoices. Optional.</t>
+        <t>Only if the book is handed over PART-USED — the first still-blank coupon. Blank = starts at series start.</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Date the book was handed over. Default = today.</t>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>active / exhausted / cancelled / lost. Default active.</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>One photo of a coupon from THIS booklet — the slip format the parser reads (Coupon No, Date, Vehicle, litres, seal) AND the dispute backup a bill is checked against later. Stored against the booklet as a coupon artifact. Put the file name (e.g. Coupon-ABC-sample.jpg) or a link here; the picture goes in the shared folder.</t>
       </text>
     </comment>
   </commentList>
@@ -434,44 +453,19 @@
     <author>Pumpini</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0">
-      <text>
-        <t>Which credit customer this booklet is issued to. Must match a company on tab 11.</t>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0">
-      <text>
-        <t>Optional printed book id / name. Free text.</t>
-      </text>
-    </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>The FIRST coupon number in the book, e.g. 17701. Ranges must not overlap another book at this outlet.</t>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>The LAST coupon number in the book, e.g. 17800. Must be ≥ series start.</t>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <t>Only if the book is handed over PART-USED — the first still-blank coupon. Blank = starts at series start.</t>
+        <t>piece / litre / kg. Default piece.</t>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>Date the book was handed over. Default = today.</t>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>active / exhausted / cancelled / lost. Default active.</t>
+        <t>Default 18.</t>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>One photo of a coupon from THIS booklet — the slip format the parser reads (Coupon No, Date, Vehicle, litres, seal) AND the dispute backup a bill is checked against later. Stored against the booklet as a coupon artifact. Put the file name (e.g. Coupon-ABC-sample.jpg) or a link here; the picture goes in the shared folder.</t>
+        <t>Units in stock at go-live.</t>
       </text>
     </comment>
   </commentList>
@@ -484,49 +478,59 @@
     <author>Pumpini</author>
   </authors>
   <commentList>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>Cash short/over alert threshold. Default 50.</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Only needed if you switch geofenced attendance on.</t>
+      </text>
+    </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>piece / litre / kg. Default piece.</t>
+        <t>Only needed if you switch geofenced attendance on.</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>Default 500 m.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>yes/no. Default no.</t>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>Default 18.</t>
+        <t>yes/no — mask shift sales from the manager. Default no.</t>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>Dip-vs-book tolerance. Default 0.75 (%).</t>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>Units in stock at go-live.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Pumpini</author>
-  </authors>
-  <commentList>
-    <comment ref="A4" authorId="0" shapeId="0">
-      <text>
-        <t>Must match a company on tab 11.</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
-      <text>
-        <t>10 digits.</t>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>e.g. TS09AB1234.</t>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
-      <text>
-        <t>Max value per fuelling. Optional.</t>
+        <t>Default 0.50 (%).</t>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <t>Minimum litres tolerance. Default 20.</t>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="0" shapeId="0">
+      <text>
+        <t>Alert if no bank deposit in N days. Default 2.</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>Only if you export to Tally. Company name as it appears in Tally.</t>
       </text>
     </comment>
   </commentList>
@@ -551,82 +555,42 @@
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Street address.</t>
+        <t>Street address. PRINTED ON YOUR GST INVOICES.</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>Printed on your GST invoices.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>Printed on your GST invoices (place of supply).</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Printed on your GST invoices.</t>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>15-char GST number. Used on invoices.</t>
+        <t>15-char GST number. Printed on your GST invoices. Your PAN is already inside it (characters 3-12), so we do not ask for PAN separately.</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>10 digits. Where owner alerts and daily reports go.</t>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <t>Manager screen language. en / te / ta / hi. Default en.</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>10 digits. Where owner alerts/reports go.</t>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="0" shapeId="0">
-      <text>
-        <t>Manager UI language. en / te / ta / hi. Default en.</t>
-      </text>
-    </comment>
-    <comment ref="M4" authorId="0" shapeId="0">
-      <text>
-        <t>Prefix on GST invoice numbers. Default INV.</t>
-      </text>
-    </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
-      <text>
-        <t>Cash short/over alert threshold. Default 50.</t>
-      </text>
-    </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
-      <text>
-        <t>For geofenced attendance. Optional.</t>
-      </text>
-    </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
-      <text>
-        <t>For geofenced attendance. Optional.</t>
-      </text>
-    </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
-      <text>
-        <t>Default 500 m.</t>
-      </text>
-    </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
-      <text>
-        <t>yes/no. Default no.</t>
-      </text>
-    </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
-      <text>
-        <t>yes/no — mask shift sales from the manager. Default no.</t>
-      </text>
-    </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
-      <text>
-        <t>Dip-vs-book tolerance. Default 0.75 (%).</t>
-      </text>
-    </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
-      <text>
-        <t>Default 0.50 (%).</t>
-      </text>
-    </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
-      <text>
-        <t>Minimum litres tolerance. Default 20.</t>
-      </text>
-    </comment>
-    <comment ref="W4" authorId="0" shapeId="0">
-      <text>
-        <t>Alert if no bank deposit in N days. Default 2.</t>
-      </text>
-    </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
-      <text>
-        <t>Company name as it appears in Tally. Optional.</t>
+        <t>Prefix on your GST invoice numbers. Default INV.</t>
       </text>
     </comment>
   </commentList>
@@ -639,24 +603,19 @@
     <author>Pumpini</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0">
-      <text>
-        <t>e.g. 'pro' or 'lite'. A name containing 'lite' unlocks the Lite feature set only.</t>
-      </text>
-    </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>active / suspended / cancelled. Default active.</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
-      <text>
-        <t>Default = today.</t>
+        <t>10 digits. Login ID — must be unique.</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>Blank = open-ended / current subscription.</t>
+        <t>manager = runs this outlet · cco = back-office across the owner group.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>Leave blank for 'Welcome@123' (forced reset on first login).</t>
       </text>
     </comment>
   </commentList>
@@ -671,17 +630,12 @@
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>10 digits. Login ID — must be unique.</t>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>manager = runs this outlet · cco = back-office across the owner group.</t>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <t>Leave blank for 'Welcome@123' (forced reset on first login).</t>
+        <t>10 digits. Login ID — must be unique. Both name and mobile are required.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>en / te / ta / hi. Default en.</t>
       </text>
     </comment>
   </commentList>
@@ -694,14 +648,34 @@
     <author>Pumpini</author>
   </authors>
   <commentList>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>1, 2, 3 … Unique within the outlet. Nozzles refer to this.</t>
+      </text>
+    </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>10 digits. Login ID — must be unique. Both name and mobile are required.</t>
+        <t>petrol / diesel / premium_petrol / cng / xp95 / speed / power.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>en / te / ta / hi. Default en.</t>
+        <t>Nominal tank capacity in litres.</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>Dip-verified litres in the tank at go-live.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>e.g. petrol ≈ 0.735, diesel ≈ 0.825. Optional but recommended.</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Photo of the gauge / ATG (Pinelabs) screen showing this tank's opening stock at go-live. Put the file name (e.g. Tank-1-gauge.jpg) or a link here; the picture goes in the shared folder. Recommended.</t>
       </text>
     </comment>
   </commentList>
@@ -716,32 +690,22 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>1, 2, 3 … Unique within the outlet. Nozzles refer to this.</t>
+        <t>The number painted on the unit, e.g. 1, 2. Nozzles refer to this.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>petrol / diesel / premium_petrol / cng / xp95 / speed / power.</t>
+        <t>REQUIRED for slip scanning. A photo of the slip this dispenser (Pinelabs / totalizer) prints. Setup OCRs it to read the SERIAL, MODEL and nozzle lines, and keeps it as the reference print-format. Put the file name (e.g. Pump-1-slip.jpg) or a link here; the picture goes in the shared folder.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Nominal tank capacity in litres.</t>
+        <t>OCR reads this from the slip photo — leave blank if the photo is clear. The owner confirms it before it saves.</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>Dip-verified litres in the tank at go-live.</t>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <t>e.g. petrol ≈ 0.735, diesel ≈ 0.825. Optional but recommended.</t>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
-      <text>
-        <t>Photo of the gauge / ATG (Pinelabs) screen showing this tank's opening stock at go-live. Put the file name (e.g. Tank-1-gauge.jpg) or a link here; the picture goes in the shared folder. Recommended.</t>
+        <t>OCR reads this from the slip photo too. Leave blank if the photo is clear.</t>
       </text>
     </comment>
   </commentList>
@@ -756,22 +720,27 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>The number painted on the unit, e.g. 1, 2. Nozzles refer to this.</t>
+        <t>Label printed on the nozzle, e.g. 1, 2, 3A. Convention '1.1' = pump1.nozzle1.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>REQUIRED for slip scanning. A photo of the slip this dispenser (Pinelabs / totalizer) prints. Setup OCRs it to read the SERIAL, MODEL and nozzle lines, and keeps it as the reference print-format. Put the file name (e.g. Pump-1-slip.jpg) or a link here; the picture goes in the shared folder.</t>
+        <t>Which tank feeds this nozzle. Must exist on the Tanks tab.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>OCR reads this from the slip photo — leave blank if the photo is clear. The owner confirms it before it saves.</t>
+        <t>Should match the tank's fuel.</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>OCR reads this from the slip photo too. Leave blank if the photo is clear.</t>
+        <t>OPTIONAL. Which dispenser (tab 6) this nozzle sits on.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>OPTIONAL. The line this nozzle prints on the dispenser's totalizer slip.</t>
       </text>
     </comment>
   </commentList>
@@ -786,27 +755,12 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>Label printed on the nozzle, e.g. 1, 2, 3A. Convention '1.1' = pump1.nozzle1.</t>
+        <t>petrol / diesel / premium_petrol / cng / xp95 / speed / power.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>Which tank feeds this nozzle. Must exist on the Tanks tab.</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
-      <text>
-        <t>Should match the tank's fuel.</t>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>OPTIONAL. Which dispenser (tab 7) this nozzle sits on.</t>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <t>OPTIONAL. The line this nozzle prints on the dispenser's totalizer slip.</t>
+        <t>Opening per-litre price.</t>
       </text>
     </comment>
   </commentList>
@@ -821,12 +775,22 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>petrol / diesel / premium_petrol / cng / xp95 / speed / power.</t>
+        <t>1, 2 or 3.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>Opening per-litre price.</t>
+        <t>e.g. Morning / Afternoon / Night.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>24-hour HH:MM, e.g. 06:00.</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>24-hour HH:MM, e.g. 14:00.</t>
       </text>
     </comment>
   </commentList>
@@ -1122,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D43"/>
+  <dimension ref="B2:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1172,161 +1136,161 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>The station itself + all station settings (GST, address, geofence, tolerances, blind-drop, alerts).</t>
+          <t>The station: name, oil company, address and GSTIN as they should print on your invoices.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3. Subscription</t>
+          <t>3. Staff (Mgr/CCO)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>The plan the outlet runs on (drives the feature ceiling / entitlement).</t>
+          <t>Managers and back-office (CCO) logins linked to this outlet.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4. Staff (Mgr/CCO)</t>
+          <t>4. Attendants</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Managers and back-office (CCO) logins linked to this outlet.</t>
+          <t>The operators who run the pumps and settle shifts. Name + mobile is enough.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5. Attendants</t>
+          <t>5. Tanks</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>The operators who run the pumps and settle shifts. Name + mobile is enough.</t>
+          <t>Underground tanks: number, fuel, capacity, opening stock, density + opening gauge/ATG photo.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6. Tanks</t>
+          <t>6. Pumps</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Underground tanks: number, fuel, capacity, opening stock, density + opening gauge/ATG photo.</t>
+          <t>The dispenser machines + their SAMPLE TOTALIZER-SLIP PHOTO (required for slip scanning).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>7. Pumps</t>
+          <t>7. Nozzles</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>The dispenser machines + their SAMPLE TOTALIZER-SLIP PHOTO (required for slip scanning).</t>
+          <t>Each nozzle mapped to its tank + fuel (and optionally its dispenser / slip line).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8. Nozzles</t>
+          <t>8. Fuel Prices</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Each nozzle mapped to its tank + fuel (and optionally its dispenser / slip line).</t>
+          <t>Opening per-litre price for each fuel this outlet sells.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>9. Fuel Prices</t>
+          <t>9. Shift Timings</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Opening per-litre price for each fuel this outlet sells.</t>
+          <t>The 1–3 daily shift windows the outlet runs.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>10. Shift Timings</t>
+          <t>10. Credit Customers</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>The 1–3 daily shift windows the outlet runs.</t>
+          <t>Corporate / credit accounts and their go-live opening balances.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>11. Credit Customers</t>
+          <t>11. Credit Slip Books</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Corporate / credit accounts and their go-live opening balances.</t>
+          <t>Coupon booklets allocated to a credit customer: series range + a sample coupon photo.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>12. Credit Slip Books</t>
+          <t>12. Products</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Coupon booklets allocated to a credit customer: series range + a sample coupon photo.</t>
+          <t>OPTIONAL — shop / lubricant products, only if the outlet uses the store module.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>13. Products</t>
+          <t>13. Defaults</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>OPTIONAL — shop / lubricant products, only if the outlet uses the store module.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>14. Corporate Drivers</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>OPTIONAL — drivers/vehicles under a credit customer (RFID/FastTag fleets).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+          <t>OPTIONAL — LEAVE BLANK. Alert and tolerance defaults; we set these and you can change them in Settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Images &amp; photos  (READ THIS)</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Some of the setup CANNOT be done from text alone — it needs photographs. A spreadsheet can't hold images, so the sheet holds a FILE-NAME (or a link) per photo and you supply the actual pictures alongside it.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="B22" s="8" t="inlineStr">
@@ -1336,7 +1300,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Some of the setup CANNOT be done from text alone — it needs photographs. A spreadsheet can't hold images, so the sheet holds a FILE-NAME (or a link) per photo and you supply the actual pictures alongside it.</t>
+          <t>How: put every photo in ONE shared folder (Google Drive / OneDrive) and name each file after its row — e.g. 'Pump-1-slip.jpg', 'Tank-1-gauge.jpg'. Type that file name (or a direct link) into the green photo column. Then share the folder link with us.</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1312,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>How: put every photo in ONE shared folder (Google Drive / OneDrive) and name each file after its row — e.g. 'Pump-1-slip.jpg', 'Tank-1-gauge.jpg'. Type that file name (or a direct link) into the green photo column. Then share the folder link with us.</t>
+          <t>Pump sample slip (green column on tab 6) — REQUIRED for slip scanning. A photo of the totalizer slip the dispenser prints. Setup runs OCR on it to read the pump SERIAL, MODEL and which line is which nozzle, and keeps it as the reference print-format for every future settlement scan. Leave Serial/Model blank if the photo is clear — OCR fills them, and the owner confirms before it's saved.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1324,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Pump sample slip (green column on tab 7) — REQUIRED for slip scanning. A photo of the totalizer slip the dispenser prints. Setup runs OCR on it to read the pump SERIAL, MODEL and which line is which nozzle, and keeps it as the reference print-format for every future settlement scan. Leave Serial/Model blank if the photo is clear — OCR fills them, and the owner confirms before it's saved.</t>
+          <t>Tank gauge / ATG (Pinelabs) screen (green column on tab 5) — recommended at go-live. A photo of the gauge screen showing opening stock; it's the picture behind the first wet-stock figure the outlet is measured against.</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1336,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tank gauge / ATG (Pinelabs) screen (green column on tab 6) — recommended at go-live. A photo of the gauge screen showing opening stock; it's the picture behind the first wet-stock figure the outlet is measured against.</t>
+          <t>Credit-coupon sample (green column on tab 11) — one photo per credit customer's booklet. It records the SLIP FORMAT the coupon parser will read (Coupon No, Date, Vehicle, litres, seal). A sample per customer/dealer, not per coupon — the live coupons are photographed per sale in the app.</t>
         </is>
       </c>
     </row>
@@ -1384,77 +1348,77 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Credit-coupon sample (green column on tab 12) — one photo per credit customer's booklet. It records the SLIP FORMAT the coupon parser will read (Coupon No, Date, Vehicle, litres, seal). A sample per customer/dealer, not per coupon — the live coupons are photographed per sale in the app.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="B27" s="8" t="inlineStr">
+          <t>Nozzle meter photos are NOT a setup item — those are captured per shift during settlement, in the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="11" t="inlineStr"/>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Yellow cell — A value YOU fill in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="B30" s="13" t="inlineStr"/>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Blue header (white text) — REQUIRED column — the row is rejected without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="B31" s="14" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Grey header (white text) — Optional column — safe to leave blank; a sensible default applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Green header + green cell — A PHOTO reference — put the file name / link here; the picture goes in the shared folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="B33" s="16" t="inlineStr"/>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Italic grey row — An EXAMPLE row showing the expected format. Delete it before import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>House rules</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Nozzle meter photos are NOT a setup item — those are captured per shift during settlement, in the app.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="11" t="inlineStr"/>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Yellow cell — A value YOU fill in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="13" t="inlineStr"/>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Blue header (white text) — REQUIRED column — the row is rejected without it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="14" t="inlineStr"/>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Grey header (white text) — Optional column — safe to leave blank; a sensible default applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="15" t="inlineStr"/>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>Green header + green cell — A PHOTO reference — put the file name / link here; the picture goes in the shared folder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="B34" s="16" t="inlineStr"/>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Italic grey row — An EXAMPLE row showing the expected format. Delete it before import.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>House rules</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Mobile numbers: 10 Indian digits (e.g. 9876543210). +91 is added automatically. A phone is a login ID — it must be unique.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="17" t="inlineStr">
@@ -1464,7 +1428,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Mobile numbers: 10 Indian digits (e.g. 9876543210). +91 is added automatically. A phone is a login ID — it must be unique.</t>
+          <t>Dates: DD-MMM-YYYY (e.g. 05-Aug-2026). India is DD/MM — never MM/DD.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1440,7 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Dates: DD-MMM-YYYY (e.g. 05-Aug-2026). India is DD/MM — never MM/DD.</t>
+          <t>Times: 24-hour HH:MM (e.g. 06:00, 14:00, 22:00).</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1452,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Times: 24-hour HH:MM (e.g. 06:00, 14:00, 22:00).</t>
+          <t>Fuel types must be one of: petrol, diesel, premium_petrol, cng, xp95, speed, power. Use the SAME spelling on Tanks, Nozzles and Fuel Prices.</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1464,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Fuel types must be one of: petrol, diesel, premium_petrol, cng, xp95, speed, power. Use the SAME spelling on Tanks, Nozzles and Fuel Prices.</t>
+          <t>New staff/owners get the starter password 'Welcome@123' and are forced to reset on first login — leave the password blank to use it.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1476,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>New staff/owners get the starter password 'Welcome@123' and are forced to reset on first login — leave the password blank to use it.</t>
+          <t>Money is in ₹. Opening stock is in litres. Density is kg/L (e.g. petrol ≈ 0.735, diesel ≈ 0.825).</t>
         </is>
       </c>
     </row>
@@ -1523,18 +1487,6 @@
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Money is in ₹. Opening stock is in litres. Density is kg/L (e.g. petrol ≈ 0.735, diesel ≈ 0.825).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>This sheet COLLECTS the data + photo references; a superadmin runs the actual go-live. Nothing here writes to production by itself.</t>
         </is>
@@ -1545,21 +1497,21 @@
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C43:D43"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1567,104 +1519,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>9 · Opening Fuel Prices</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>The per-litre selling price of each fuel at go-live. One row per fuel type the outlet sells. Prices are updated daily in-app after go-live; this just seeds the first price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>Fuel type
-(fuel_prices.fuel_type)</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>Price ₹/L
-(fuel_prices.price)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>petrol</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>105.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="A6:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
-      <formula1>"petrol,diesel,premium_petrol,cng,xp95,speed,power"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1682,7 +1536,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>10 · Shift Timings</t>
+          <t>9 · Shift Timings</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1791,7 +1645,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>11 · Credit (Corporate) Customers</t>
+          <t>10 · Credit (Corporate) Customers</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2001,14 +1855,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>12 · Credit Slip Books (coupon booklets)</t>
+          <t>11 · Credit Slip Books (coupon booklets)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>The pre-printed coupon booklets allocated to a credit customer. One row per booklet. The coupon series range is recorded so a missing / re-used coupon can be caught; the green column holds a sample coupon photo that records the slip format. Company name must match a row on tab 11.</t>
+          <t>The pre-printed coupon booklets allocated to a credit customer. One row per booklet. The coupon series range is recorded so a missing / re-used coupon can be caught; the green column holds a sample coupon photo that records the slip format. Company name must match a row on tab 10.</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2253,7 +2107,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>13 · Products  (OPTIONAL — only if the store module is used)</t>
+          <t>12 · Products  (OPTIONAL — only if the store module is used)</t>
         </is>
       </c>
     </row>
@@ -2498,103 +2352,153 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>14 · Corporate Drivers / Vehicles  (OPTIONAL)</t>
+          <t>13 · Defaults  (OPTIONAL — LEAVE THIS TAB BLANK)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Drivers and vehicles under a credit customer — used by RFID / FastTag fleet fuelling. The 'Company name' must match a row on the Credit Customers tab.</t>
+          <t>You do not need to fill anything in here. These are Pumpini's alert and tolerance settings; we apply the defaults shown in the example row at go-live and you can change any of them yourself later in Settings. Fill a cell only if you already know you want a different value.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>Company name
-(→ Credit Customers)</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>Driver name
-(corporate_drivers.name)</t>
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Variance threshold ₹
+(variance_threshold)</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Latitude
+(latitude)</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Driver mobile
-(phone)</t>
+          <t>Longitude
+(longitude)</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>Vehicle number
-(vehicle_number)</t>
+          <t>Geofence radius m
+(geo_fence_radius)</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>FastTag / RFID id
-(fasttag_id)</t>
+          <t>Geofence on?
+(geo_fence_enabled)</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>Per-fill limit ₹
-(per_fill_limit)</t>
+          <t>Manager blind-drop?
+(manager_blind_drop)</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Stock tol % petrol
+(stock_tol_pct_petrol)</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>Stock tol % diesel
+(stock_tol_pct_diesel)</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>Stock tol floor L
+(stock_tol_floor_ltrs)</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Deposit alert days
+(deposit_alert_days)</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Tally company
+(tally_company_name)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>ABC Logistics Pvt Ltd</t>
-        </is>
+      <c r="A5" s="22" t="n">
+        <v>50</v>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>Rajan M</t>
+          <t>17.5810</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>9876000001</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>TS09AB1234</t>
-        </is>
+          <t>78.4990</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>500</v>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>FT123456</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>5000</v>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H5" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="22" t="inlineStr">
+        <is>
+          <t>Kamala Highway HPCL</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2604,6 +2508,11 @@
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -2612,108 +2521,25 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="11" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E6:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -2894,23 +2720,9 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2972,106 +2784,22 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>PAN
-(station_settings.pan)</t>
-        </is>
-      </c>
-      <c r="I4" s="21" t="inlineStr">
-        <is>
-          <t>TAN
-(station_settings.tan)</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
           <t>Owner WhatsApp
 (owner_whatsapp)</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
-        <is>
-          <t>Owner email
-(station_settings.owner_email)</t>
-        </is>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>Language
 (language)</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>Invoice prefix
 (invoice_prefix)</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t>Variance threshold ₹
-(variance_threshold)</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="inlineStr">
-        <is>
-          <t>Latitude
-(latitude)</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t>Longitude
-(longitude)</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr">
-        <is>
-          <t>Geofence radius m
-(geo_fence_radius)</t>
-        </is>
-      </c>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t>Geofence on?
-(geo_fence_enabled)</t>
-        </is>
-      </c>
-      <c r="S4" s="21" t="inlineStr">
-        <is>
-          <t>Manager blind-drop?
-(manager_blind_drop)</t>
-        </is>
-      </c>
-      <c r="T4" s="21" t="inlineStr">
-        <is>
-          <t>Stock tol % petrol
-(stock_tol_pct_petrol)</t>
-        </is>
-      </c>
-      <c r="U4" s="21" t="inlineStr">
-        <is>
-          <t>Stock tol % diesel
-(stock_tol_pct_diesel)</t>
-        </is>
-      </c>
-      <c r="V4" s="21" t="inlineStr">
-        <is>
-          <t>Stock tol floor L
-(stock_tol_floor_ltrs)</t>
-        </is>
-      </c>
-      <c r="W4" s="21" t="inlineStr">
-        <is>
-          <t>Deposit alert days
-(deposit_alert_days)</t>
-        </is>
-      </c>
-      <c r="X4" s="21" t="inlineStr">
-        <is>
-          <t>Tally company
-(tally_company_name)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
@@ -3111,75 +2839,17 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>ABCDE1234F</t>
+          <t>9876500001</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
         <is>
-          <t>HYDK12345A</t>
+          <t>en</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>9876500001</t>
-        </is>
-      </c>
-      <c r="K5" s="22" t="inlineStr">
-        <is>
-          <t>owner@kamala.in</t>
-        </is>
-      </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="M5" s="22" t="inlineStr">
-        <is>
           <t>KAM</t>
-        </is>
-      </c>
-      <c r="N5" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="O5" s="22" t="inlineStr">
-        <is>
-          <t>17.5810</t>
-        </is>
-      </c>
-      <c r="P5" s="22" t="inlineStr">
-        <is>
-          <t>78.4990</t>
-        </is>
-      </c>
-      <c r="Q5" s="22" t="n">
-        <v>500</v>
-      </c>
-      <c r="R5" s="22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S5" s="22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="T5" s="22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U5" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V5" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="W5" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" s="22" t="inlineStr">
-        <is>
-          <t>Kamala Highway HPCL</t>
         </is>
       </c>
     </row>
@@ -3194,20 +2864,6 @@
       <c r="H6" s="11" t="n"/>
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="11" t="n"/>
-      <c r="Q6" s="11" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="11" t="n"/>
-      <c r="T6" s="11" t="n"/>
-      <c r="U6" s="11" t="n"/>
-      <c r="V6" s="11" t="n"/>
-      <c r="W6" s="11" t="n"/>
-      <c r="X6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -3220,20 +2876,6 @@
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="11" t="n"/>
-      <c r="Q7" s="11" t="n"/>
-      <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="11" t="n"/>
-      <c r="U7" s="11" t="n"/>
-      <c r="V7" s="11" t="n"/>
-      <c r="W7" s="11" t="n"/>
-      <c r="X7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -3246,20 +2888,6 @@
       <c r="H8" s="11" t="n"/>
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="n"/>
-      <c r="Q8" s="11" t="n"/>
-      <c r="R8" s="11" t="n"/>
-      <c r="S8" s="11" t="n"/>
-      <c r="T8" s="11" t="n"/>
-      <c r="U8" s="11" t="n"/>
-      <c r="V8" s="11" t="n"/>
-      <c r="W8" s="11" t="n"/>
-      <c r="X8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -3272,35 +2900,15 @@
       <c r="H9" s="11" t="n"/>
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="11" t="n"/>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="11" t="n"/>
-      <c r="U9" s="11" t="n"/>
-      <c r="V9" s="11" t="n"/>
-      <c r="W9" s="11" t="n"/>
-      <c r="X9" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:X2"/>
     <mergeCell ref="A1:X1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="L6:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="I6:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
       <formula1>"en,te,ta,hi"</formula1>
-    </dataValidation>
-    <dataValidation sqref="R6:R200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation sqref="S6:S200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
-      <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3309,115 +2917,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>3 · Subscription / Plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>The plan this outlet runs on. The plan drives the feature ceiling (entitlement): a plan whose name contains 'lite' → the Lite feature set, otherwise the full Pumpini set. One row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>Plan
-(station_subscriptions.plan)</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Status
-(status)</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Start date
-(start_date)</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>End date
-(end_date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>pro</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>05-Aug-2026</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="A6:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
-      <formula1>"pro,lite,trial"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B6:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
-      <formula1>"active,suspended,cancelled"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3436,7 +2935,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>4 · Managers &amp; Back-office (CCO)</t>
+          <t>3 · Managers &amp; Back-office (CCO)</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3604,7 +3103,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>5 · Attendants (operators)</t>
+          <t>4 · Attendants (operators)</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3787,14 +3286,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>6 · Tanks</t>
+          <t>5 · Tanks</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>One row per underground tank. 'Opening stock' is the dip-verified stock at go-live. Tank number is referenced by nozzles on tab 8. The green column is the file name / link of the opening gauge photo.</t>
+          <t>One row per underground tank. 'Opening stock' is the dip-verified stock at go-live. Tank number is referenced by nozzles on tab 7. The green column is the file name / link of the opening gauge photo.</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3990,7 +3489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>7 · Pumps / Dispensers  (+ sample slip photo)</t>
+          <t>6 · Pumps / Dispensers  (+ sample slip photo)</t>
         </is>
       </c>
     </row>
@@ -4132,7 +3631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4151,7 +3650,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>8 · Nozzles</t>
+          <t>7 · Nozzles</t>
         </is>
       </c>
     </row>
@@ -4342,4 +3841,102 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>8 · Opening Fuel Prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>The per-litre selling price of each fuel at go-live. One row per fuel type the outlet sells. Prices are updated daily in-app after go-live; this just seeds the first price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Fuel type
+(fuel_prices.fuel_type)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Price ₹/L
+(fuel_prices.price)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>petrol</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="A6:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from list" error="Pick a value from the list." type="list">
+      <formula1>"petrol,diesel,premium_petrol,cng,xp95,speed,power"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>